--- a/派工品項.xlsx
+++ b/派工品項.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.0.88\fax\理貨部\姿旻\2026\代辦事項\vs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\vs\SCA(理貨派工)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FE7FFAF7-418A-48FF-924F-A3807B96455C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61CC4FF9-3C40-4C89-8739-C824412DA1AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{42C09545-1C84-4FC4-A6F8-B127EEAED499}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{42C09545-1C84-4FC4-A6F8-B127EEAED499}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="169">
   <si>
     <t>品項代號</t>
   </si>
@@ -632,6 +632,10 @@
       </rPr>
       <t>托盤］</t>
     </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>大買家；乾、拿最新日期</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -866,9 +870,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 佈景主題">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 主題">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -906,7 +910,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1012,7 +1016,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1154,7 +1158,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1163,15 +1167,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DF569F7-F3AC-42BF-88F9-E327F95E867A}">
   <dimension ref="A1:F96"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="33.625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="33.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.44140625" customWidth="1"/>
+    <col min="5" max="6" width="9.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1191,7 +1196,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A2" s="5" t="s">
         <v>5</v>
       </c>
@@ -1205,7 +1210,7 @@
       <c r="E2" s="8"/>
       <c r="F2" s="8"/>
     </row>
-    <row r="3" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A3" s="9" t="s">
         <v>8</v>
       </c>
@@ -1223,7 +1228,7 @@
         <v>20.399999999999999</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A4" s="9" t="s">
         <v>10</v>
       </c>
@@ -1241,7 +1246,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A5" s="9" t="s">
         <v>12</v>
       </c>
@@ -1259,7 +1264,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A6" s="9" t="s">
         <v>14</v>
       </c>
@@ -1277,7 +1282,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A7" s="9" t="s">
         <v>16</v>
       </c>
@@ -1295,7 +1300,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A8" s="13" t="s">
         <v>18</v>
       </c>
@@ -1313,7 +1318,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A9" s="9" t="s">
         <v>20</v>
       </c>
@@ -1331,7 +1336,7 @@
         <v>48.6</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A10" s="9" t="s">
         <v>23</v>
       </c>
@@ -1351,7 +1356,7 @@
         <v>30.6</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A11" s="9" t="s">
         <v>26</v>
       </c>
@@ -1371,7 +1376,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A12" s="9" t="s">
         <v>28</v>
       </c>
@@ -1389,7 +1394,7 @@
         <v>25.2</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A13" s="9" t="s">
         <v>31</v>
       </c>
@@ -1407,7 +1412,7 @@
         <v>9.6</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A14" s="9" t="s">
         <v>34</v>
       </c>
@@ -1425,7 +1430,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A15" s="9" t="s">
         <v>36</v>
       </c>
@@ -1443,7 +1448,7 @@
         <v>25.2</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A16" s="9" t="s">
         <v>38</v>
       </c>
@@ -1461,7 +1466,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A17" s="9" t="s">
         <v>40</v>
       </c>
@@ -1479,7 +1484,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A18" s="9" t="s">
         <v>40</v>
       </c>
@@ -1499,7 +1504,7 @@
         <v>97.2</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A19" s="9" t="s">
         <v>43</v>
       </c>
@@ -1517,7 +1522,7 @@
         <v>25.2</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="20" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A20" s="9" t="s">
         <v>45</v>
       </c>
@@ -1537,7 +1542,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A21" s="9" t="s">
         <v>45</v>
       </c>
@@ -1557,7 +1562,7 @@
         <v>88.2</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="22" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A22" s="9" t="s">
         <v>45</v>
       </c>
@@ -1577,7 +1582,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="23" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A23" s="9" t="s">
         <v>50</v>
       </c>
@@ -1595,7 +1600,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="24" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A24" s="9" t="s">
         <v>53</v>
       </c>
@@ -1615,7 +1620,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="25" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A25" s="9" t="s">
         <v>54</v>
       </c>
@@ -1635,7 +1640,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="26" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A26" s="9" t="s">
         <v>56</v>
       </c>
@@ -1653,7 +1658,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="27" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A27" s="9" t="s">
         <v>57</v>
       </c>
@@ -1671,7 +1676,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="28" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A28" s="9" t="s">
         <v>58</v>
       </c>
@@ -1689,7 +1694,7 @@
         <v>49.8</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="29" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A29" s="9" t="s">
         <v>60</v>
       </c>
@@ -1707,7 +1712,7 @@
         <v>88.8</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="30" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A30" s="9" t="s">
         <v>62</v>
       </c>
@@ -1725,7 +1730,7 @@
         <v>79.8</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="31" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A31" s="9" t="s">
         <v>65</v>
       </c>
@@ -1743,7 +1748,7 @@
         <v>49.2</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="32" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A32" s="9" t="s">
         <v>67</v>
       </c>
@@ -1761,7 +1766,7 @@
         <v>115.8</v>
       </c>
     </row>
-    <row r="33" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="33" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A33" s="9" t="s">
         <v>67</v>
       </c>
@@ -1772,7 +1777,7 @@
         <v>48</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="E33" s="12">
         <v>2.58</v>
@@ -1782,7 +1787,7 @@
         <v>154.80000000000001</v>
       </c>
     </row>
-    <row r="34" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="34" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A34" s="9" t="s">
         <v>69</v>
       </c>
@@ -1800,7 +1805,7 @@
         <v>40.200000000000003</v>
       </c>
     </row>
-    <row r="35" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="35" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A35" s="9" t="s">
         <v>72</v>
       </c>
@@ -1818,7 +1823,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="36" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="36" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A36" s="9" t="s">
         <v>75</v>
       </c>
@@ -1836,7 +1841,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="37" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="37" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A37" s="9" t="s">
         <v>78</v>
       </c>
@@ -1854,7 +1859,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="38" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="38" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A38" s="9" t="s">
         <v>80</v>
       </c>
@@ -1872,7 +1877,7 @@
         <v>83.4</v>
       </c>
     </row>
-    <row r="39" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="39" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A39" s="13" t="s">
         <v>80</v>
       </c>
@@ -1890,7 +1895,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="40" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A40" s="13" t="s">
         <v>80</v>
       </c>
@@ -1908,7 +1913,7 @@
         <v>13.2</v>
       </c>
     </row>
-    <row r="41" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="41" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A41" s="9" t="s">
         <v>84</v>
       </c>
@@ -1926,7 +1931,7 @@
         <v>47.4</v>
       </c>
     </row>
-    <row r="42" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="42" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A42" s="9" t="s">
         <v>86</v>
       </c>
@@ -1944,7 +1949,7 @@
         <v>51.6</v>
       </c>
     </row>
-    <row r="43" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="43" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A43" s="9" t="s">
         <v>88</v>
       </c>
@@ -1962,7 +1967,7 @@
         <v>51.6</v>
       </c>
     </row>
-    <row r="44" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="44" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A44" s="9" t="s">
         <v>90</v>
       </c>
@@ -1980,7 +1985,7 @@
         <v>51.6</v>
       </c>
     </row>
-    <row r="45" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="45" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A45" s="9" t="s">
         <v>92</v>
       </c>
@@ -1998,7 +2003,7 @@
         <v>13.8</v>
       </c>
     </row>
-    <row r="46" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="46" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A46" s="9" t="s">
         <v>94</v>
       </c>
@@ -2016,7 +2021,7 @@
         <v>13.8</v>
       </c>
     </row>
-    <row r="47" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="47" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A47" s="9" t="s">
         <v>96</v>
       </c>
@@ -2034,7 +2039,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="48" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="48" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A48" s="9" t="s">
         <v>98</v>
       </c>
@@ -2052,7 +2057,7 @@
         <v>51.3</v>
       </c>
     </row>
-    <row r="49" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="49" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A49" s="9" t="s">
         <v>101</v>
       </c>
@@ -2070,7 +2075,7 @@
         <v>60.6</v>
       </c>
     </row>
-    <row r="50" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="50" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A50" s="15" t="s">
         <v>101</v>
       </c>
@@ -2089,7 +2094,7 @@
         <v>26.4</v>
       </c>
     </row>
-    <row r="51" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="51" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A51" s="9" t="s">
         <v>105</v>
       </c>
@@ -2107,7 +2112,7 @@
         <v>79.8</v>
       </c>
     </row>
-    <row r="52" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="52" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A52" s="9" t="s">
         <v>107</v>
       </c>
@@ -2125,7 +2130,7 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="53" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="53" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A53" s="9" t="s">
         <v>109</v>
       </c>
@@ -2143,7 +2148,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="54" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="54" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A54" s="5" t="s">
         <v>111</v>
       </c>
@@ -2157,7 +2162,7 @@
       <c r="E54" s="8"/>
       <c r="F54" s="8"/>
     </row>
-    <row r="55" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="55" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A55" s="9" t="s">
         <v>114</v>
       </c>
@@ -2175,7 +2180,7 @@
         <v>25.8</v>
       </c>
     </row>
-    <row r="56" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="56" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A56" s="9" t="s">
         <v>116</v>
       </c>
@@ -2193,7 +2198,7 @@
         <v>66.599999999999994</v>
       </c>
     </row>
-    <row r="57" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="57" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A57" s="9" t="s">
         <v>116</v>
       </c>
@@ -2211,7 +2216,7 @@
         <v>32.4</v>
       </c>
     </row>
-    <row r="58" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="58" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A58" s="15" t="s">
         <v>119</v>
       </c>
@@ -2229,7 +2234,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="59" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="59" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A59" s="9" t="s">
         <v>121</v>
       </c>
@@ -2247,7 +2252,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="60" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="60" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A60" s="9" t="s">
         <v>121</v>
       </c>
@@ -2265,7 +2270,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="61" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="61" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A61" s="9" t="s">
         <v>123</v>
       </c>
@@ -2283,7 +2288,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="62" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="62" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A62" s="9" t="s">
         <v>123</v>
       </c>
@@ -2301,7 +2306,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="63" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="63" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A63" s="9" t="s">
         <v>125</v>
       </c>
@@ -2319,7 +2324,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="64" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="64" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A64" s="9" t="s">
         <v>125</v>
       </c>
@@ -2337,7 +2342,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="65" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="65" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A65" s="9" t="s">
         <v>127</v>
       </c>
@@ -2355,7 +2360,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="66" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="66" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A66" s="9" t="s">
         <v>127</v>
       </c>
@@ -2373,7 +2378,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="67" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="67" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A67" s="9" t="s">
         <v>129</v>
       </c>
@@ -2391,7 +2396,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="68" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="68" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A68" s="9" t="s">
         <v>129</v>
       </c>
@@ -2409,7 +2414,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="69" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="69" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A69" s="9" t="s">
         <v>131</v>
       </c>
@@ -2427,7 +2432,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="70" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="70" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A70" s="9" t="s">
         <v>131</v>
       </c>
@@ -2445,7 +2450,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="71" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="71" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A71" s="9" t="s">
         <v>133</v>
       </c>
@@ -2463,7 +2468,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="72" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="72" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A72" s="9" t="s">
         <v>133</v>
       </c>
@@ -2481,7 +2486,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="73" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="73" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A73" s="9" t="s">
         <v>135</v>
       </c>
@@ -2499,7 +2504,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="74" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="74" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A74" s="9" t="s">
         <v>135</v>
       </c>
@@ -2517,7 +2522,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="75" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="75" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A75" s="9" t="s">
         <v>135</v>
       </c>
@@ -2536,7 +2541,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="76" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="76" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A76" s="9" t="s">
         <v>138</v>
       </c>
@@ -2554,7 +2559,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="77" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="77" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A77" s="9" t="s">
         <v>138</v>
       </c>
@@ -2572,7 +2577,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="78" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="78" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A78" s="9" t="s">
         <v>140</v>
       </c>
@@ -2590,7 +2595,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="79" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="79" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A79" s="9" t="s">
         <v>140</v>
       </c>
@@ -2608,7 +2613,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="80" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="80" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A80" s="9" t="s">
         <v>140</v>
       </c>
@@ -2626,7 +2631,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="81" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="81" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A81" s="9" t="s">
         <v>140</v>
       </c>
@@ -2644,7 +2649,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="82" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="82" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A82" s="9" t="s">
         <v>140</v>
       </c>
@@ -2662,7 +2667,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="83" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="83" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A83" s="9" t="s">
         <v>140</v>
       </c>
@@ -2680,7 +2685,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="84" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="84" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A84" s="15" t="s">
         <v>140</v>
       </c>
@@ -2698,7 +2703,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="85" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="85" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A85" s="15" t="s">
         <v>140</v>
       </c>
@@ -2716,7 +2721,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="86" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="86" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A86" s="7" t="s">
         <v>145</v>
       </c>
@@ -2734,7 +2739,7 @@
         <v>58.2</v>
       </c>
     </row>
-    <row r="87" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="87" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A87" s="7" t="s">
         <v>147</v>
       </c>
@@ -2752,7 +2757,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="88" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="88" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A88" s="7" t="s">
         <v>147</v>
       </c>
@@ -2770,7 +2775,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="89" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="89" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A89" s="7" t="s">
         <v>149</v>
       </c>
@@ -2788,7 +2793,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="90" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="90" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A90" s="15" t="s">
         <v>149</v>
       </c>
@@ -2806,7 +2811,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="91" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="91" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A91" s="15" t="s">
         <v>151</v>
       </c>
@@ -2824,7 +2829,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="92" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="92" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A92" s="7" t="s">
         <v>151</v>
       </c>
@@ -2842,7 +2847,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="93" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="93" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A93" s="7" t="s">
         <v>153</v>
       </c>
@@ -2860,7 +2865,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="94" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="94" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A94" s="7" t="s">
         <v>153</v>
       </c>
@@ -2878,7 +2883,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="95" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="95" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A95" s="7"/>
       <c r="B95" s="14" t="s">
         <v>155</v>
@@ -2894,7 +2899,7 @@
         <v>470.4</v>
       </c>
     </row>
-    <row r="96" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="96" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A96" s="15" t="s">
         <v>156</v>
       </c>

--- a/派工品項.xlsx
+++ b/派工品項.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\vs\SCA(理貨派工)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61CC4FF9-3C40-4C89-8739-C824412DA1AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C2937E9-D05D-4F12-AFE9-176081EF4E34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{42C09545-1C84-4FC4-A6F8-B127EEAED499}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{42C09545-1C84-4FC4-A6F8-B127EEAED499}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="171">
   <si>
     <t>品項代號</t>
   </si>
@@ -464,12 +464,6 @@
   </si>
   <si>
     <t>巴西里［捲葉］</t>
-  </si>
-  <si>
-    <t>巴西里</t>
-  </si>
-  <si>
-    <t>歐芹［平葉巴西里］</t>
   </si>
   <si>
     <t>T15000101</t>
@@ -636,6 +630,34 @@
   </si>
   <si>
     <t>大買家；乾、拿最新日期</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>500g/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>包</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>進口600~850g間，若無法湊足請通知現場主管</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>T10000102</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>綠火焰生菜［水耕］</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1166,13 +1188,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DF569F7-F3AC-42BF-88F9-E327F95E867A}">
-  <dimension ref="A1:F96"/>
+  <dimension ref="A1:F94"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.88671875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="33.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.44140625" customWidth="1"/>
+    <col min="4" max="4" width="55.44140625" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1187,7 +1209,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E1" s="4" t="s">
         <v>3</v>
@@ -1347,7 +1369,7 @@
         <v>25</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E10" s="12">
         <v>0.51</v>
@@ -1367,7 +1389,7 @@
         <v>25</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E11" s="12">
         <v>1.3</v>
@@ -1495,7 +1517,7 @@
         <v>25</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E18" s="12">
         <v>1.62</v>
@@ -1533,7 +1555,7 @@
         <v>47</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E20" s="12">
         <v>0.9</v>
@@ -1553,7 +1575,7 @@
         <v>48</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E21" s="12">
         <v>1.47</v>
@@ -1573,7 +1595,7 @@
         <v>49</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E22" s="12">
         <v>1.1499999999999999</v>
@@ -1605,13 +1627,13 @@
         <v>53</v>
       </c>
       <c r="B24" s="19" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C24" s="11" t="s">
         <v>47</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E24" s="12">
         <v>25</v>
@@ -1631,7 +1653,7 @@
         <v>25</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E25" s="12">
         <v>1</v>
@@ -1645,7 +1667,7 @@
         <v>56</v>
       </c>
       <c r="B26" s="19" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C26" s="11" t="s">
         <v>52</v>
@@ -1663,7 +1685,7 @@
         <v>57</v>
       </c>
       <c r="B27" s="18" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C27" s="11" t="s">
         <v>30</v>
@@ -1777,7 +1799,7 @@
         <v>48</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E33" s="12">
         <v>2.58</v>
@@ -1918,7 +1940,7 @@
         <v>84</v>
       </c>
       <c r="B41" s="19" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C41" s="11" t="s">
         <v>85</v>
@@ -2452,31 +2474,31 @@
     </row>
     <row r="71" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A71" s="9" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B71" s="14" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>25</v>
+        <v>167</v>
       </c>
       <c r="D71" s="5"/>
       <c r="E71" s="12">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="F71" s="12">
-        <v>42</v>
+        <v>60</v>
       </c>
     </row>
     <row r="72" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A72" s="9" t="s">
-        <v>133</v>
+        <v>169</v>
       </c>
       <c r="B72" s="14" t="s">
-        <v>134</v>
+        <v>170</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>48</v>
+        <v>167</v>
       </c>
       <c r="D72" s="5"/>
       <c r="E72" s="12">
@@ -2488,10 +2510,10 @@
     </row>
     <row r="73" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A73" s="9" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B73" s="14" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C73" s="7" t="s">
         <v>25</v>
@@ -2506,10 +2528,10 @@
     </row>
     <row r="74" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A74" s="9" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B74" s="14" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C74" s="7" t="s">
         <v>48</v>
@@ -2530,59 +2552,59 @@
         <v>136</v>
       </c>
       <c r="C75" s="7" t="s">
-        <v>137</v>
+        <v>25</v>
       </c>
       <c r="D75" s="5"/>
       <c r="E75" s="12">
-        <v>0.25</v>
+        <v>0.7</v>
       </c>
       <c r="F75" s="12">
-        <f>E75*60</f>
-        <v>15</v>
+        <v>42</v>
       </c>
     </row>
     <row r="76" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A76" s="9" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B76" s="14" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C76" s="7" t="s">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="D76" s="5"/>
       <c r="E76" s="12">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="F76" s="12">
-        <v>42</v>
+        <v>60</v>
       </c>
     </row>
     <row r="77" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A77" s="9" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B77" s="14" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C77" s="7" t="s">
-        <v>48</v>
+        <v>137</v>
       </c>
       <c r="D77" s="5"/>
       <c r="E77" s="12">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="F77" s="12">
-        <v>60</v>
+        <f>E77*60</f>
+        <v>15</v>
       </c>
     </row>
     <row r="78" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A78" s="9" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B78" s="14" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C78" s="7" t="s">
         <v>25</v>
@@ -2597,10 +2619,10 @@
     </row>
     <row r="79" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A79" s="9" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B79" s="14" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C79" s="7" t="s">
         <v>48</v>
@@ -2618,7 +2640,7 @@
         <v>140</v>
       </c>
       <c r="B80" s="14" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C80" s="7" t="s">
         <v>25</v>
@@ -2636,7 +2658,7 @@
         <v>140</v>
       </c>
       <c r="B81" s="14" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C81" s="7" t="s">
         <v>48</v>
@@ -2654,17 +2676,17 @@
         <v>140</v>
       </c>
       <c r="B82" s="14" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="D82" s="5"/>
       <c r="E82" s="12">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="F82" s="12">
-        <v>60</v>
+        <v>42</v>
       </c>
     </row>
     <row r="83" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
@@ -2672,53 +2694,55 @@
         <v>140</v>
       </c>
       <c r="B83" s="14" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="D83" s="5"/>
       <c r="E83" s="12">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="F83" s="12">
-        <v>42</v>
+        <v>60</v>
       </c>
     </row>
     <row r="84" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="A84" s="15" t="s">
-        <v>140</v>
+      <c r="A84" s="7" t="s">
+        <v>143</v>
       </c>
       <c r="B84" s="14" t="s">
         <v>144</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="D84" s="5"/>
-      <c r="E84" s="12">
-        <v>1</v>
-      </c>
-      <c r="F84" s="12">
-        <v>60</v>
+        <v>47</v>
+      </c>
+      <c r="D84" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="E84" s="17">
+        <v>0.97</v>
+      </c>
+      <c r="F84" s="17">
+        <v>58.2</v>
       </c>
     </row>
     <row r="85" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="A85" s="15" t="s">
-        <v>140</v>
+      <c r="A85" s="7" t="s">
+        <v>145</v>
       </c>
       <c r="B85" s="14" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C85" s="7" t="s">
         <v>25</v>
       </c>
       <c r="D85" s="5"/>
       <c r="E85" s="12">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="F85" s="12">
-        <v>42</v>
+        <v>60</v>
       </c>
     </row>
     <row r="86" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
@@ -2729,14 +2753,14 @@
         <v>146</v>
       </c>
       <c r="C86" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D86" s="5"/>
-      <c r="E86" s="17">
-        <v>0.97</v>
-      </c>
-      <c r="F86" s="17">
-        <v>58.2</v>
+      <c r="E86" s="12">
+        <v>0.7</v>
+      </c>
+      <c r="F86" s="12">
+        <v>42</v>
       </c>
     </row>
     <row r="87" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
@@ -2758,7 +2782,7 @@
       </c>
     </row>
     <row r="88" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="A88" s="7" t="s">
+      <c r="A88" s="15" t="s">
         <v>147</v>
       </c>
       <c r="B88" s="14" t="s">
@@ -2776,7 +2800,7 @@
       </c>
     </row>
     <row r="89" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="A89" s="7" t="s">
+      <c r="A89" s="15" t="s">
         <v>149</v>
       </c>
       <c r="B89" s="14" t="s">
@@ -2794,7 +2818,7 @@
       </c>
     </row>
     <row r="90" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="A90" s="15" t="s">
+      <c r="A90" s="7" t="s">
         <v>149</v>
       </c>
       <c r="B90" s="14" t="s">
@@ -2812,7 +2836,7 @@
       </c>
     </row>
     <row r="91" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="A91" s="15" t="s">
+      <c r="A91" s="7" t="s">
         <v>151</v>
       </c>
       <c r="B91" s="14" t="s">
@@ -2848,78 +2872,43 @@
       </c>
     </row>
     <row r="93" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="A93" s="7" t="s">
+      <c r="A93" s="7"/>
+      <c r="B93" s="14" t="s">
         <v>153</v>
       </c>
-      <c r="B93" s="14" t="s">
-        <v>154</v>
-      </c>
       <c r="C93" s="7" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="D93" s="5"/>
       <c r="E93" s="12">
-        <v>1</v>
+        <v>7.84</v>
       </c>
       <c r="F93" s="12">
-        <v>60</v>
+        <v>470.4</v>
       </c>
     </row>
     <row r="94" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="A94" s="7" t="s">
-        <v>153</v>
+      <c r="A94" s="15" t="s">
+        <v>154</v>
       </c>
       <c r="B94" s="14" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C94" s="7" t="s">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="D94" s="5"/>
       <c r="E94" s="12">
-        <v>0.7</v>
+        <v>2.59</v>
       </c>
       <c r="F94" s="12">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="A95" s="7"/>
-      <c r="B95" s="14" t="s">
-        <v>155</v>
-      </c>
-      <c r="C95" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="D95" s="5"/>
-      <c r="E95" s="12">
-        <v>7.84</v>
-      </c>
-      <c r="F95" s="12">
-        <v>470.4</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="A96" s="15" t="s">
-        <v>156</v>
-      </c>
-      <c r="B96" s="14" t="s">
-        <v>157</v>
-      </c>
-      <c r="C96" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="D96" s="5"/>
-      <c r="E96" s="12">
-        <v>2.59</v>
-      </c>
-      <c r="F96" s="12">
-        <f>E96*60</f>
+        <f>E94*60</f>
         <v>155.39999999999998</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="257" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>